--- a/Transmission/network_model/ieee14_pvd1_2DistBus.xlsx
+++ b/Transmission/network_model/ieee14_pvd1_2DistBus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xfang\gitrepos\andes\andes\cases\ieee14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE738A0-305D-4014-8230-988EEAFB01C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77FD719-D46A-418A-B41A-19A4DC2E4134}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9456" yWindow="264" windowWidth="16920" windowHeight="11940" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Area" sheetId="8" r:id="rId7"/>
     <sheet name="Toggler" sheetId="1" r:id="rId8"/>
     <sheet name="GENROU" sheetId="9" r:id="rId9"/>
-    <sheet name="TGOV1" sheetId="10" r:id="rId10"/>
+    <sheet name="TGOV1N" sheetId="10" r:id="rId10"/>
     <sheet name="IEEEG1" sheetId="11" r:id="rId11"/>
     <sheet name="EXST1" sheetId="12" r:id="rId12"/>
     <sheet name="ESST3A" sheetId="13" r:id="rId13"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="257">
   <si>
     <t>idx</t>
   </si>
@@ -488,12 +488,6 @@
     <t>K8</t>
   </si>
   <si>
-    <t>IEEEG1_4</t>
-  </si>
-  <si>
-    <t>IEEEG1_5</t>
-  </si>
-  <si>
     <t>TR</t>
   </si>
   <si>
@@ -810,6 +804,21 @@
   </si>
   <si>
     <t>BusFreq_9</t>
+  </si>
+  <si>
+    <t>TGOV1_4</t>
+  </si>
+  <si>
+    <t>TGOV1_5</t>
+  </si>
+  <si>
+    <t>Toggler_1</t>
+  </si>
+  <si>
+    <t>GENROU</t>
+  </si>
+  <si>
+    <t>pmx</t>
   </si>
 </sst>
 </file>
@@ -1912,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -2017,7 +2026,7 @@
         <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2049,16 +2058,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>240</v>
+        <v>114</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -2082,6 +2091,88 @@
         <v>2.1</v>
       </c>
       <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0.05</v>
+      </c>
+      <c r="I5">
+        <v>1.05</v>
+      </c>
+      <c r="J5">
+        <v>0.2</v>
+      </c>
+      <c r="K5">
+        <v>0.05</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>2.1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0.05</v>
+      </c>
+      <c r="I6">
+        <v>1.05</v>
+      </c>
+      <c r="J6">
+        <v>0.2</v>
+      </c>
+      <c r="K6">
+        <v>0.05</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2.1</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
     </row>
@@ -2182,164 +2273,10 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>20</v>
-      </c>
-      <c r="J2">
-        <v>0.1</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0.2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>-1</v>
-      </c>
-      <c r="O2">
-        <v>0.95</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0.1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0.3</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>8.7200000000000006</v>
-      </c>
-      <c r="AA2">
-        <v>0.7</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>20</v>
-      </c>
-      <c r="J3">
-        <v>0.1</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0.2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>-1</v>
-      </c>
-      <c r="O3">
-        <v>0.95</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0.1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0.3</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>8.7200000000000006</v>
-      </c>
-      <c r="AA3">
-        <v>0.7</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2368,40 +2305,40 @@
         <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
@@ -2409,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
         <v>113</v>
@@ -2484,67 +2421,67 @@
         <v>116</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -2552,13 +2489,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
         <v>112</v>
@@ -2632,13 +2569,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E3" t="s">
         <v>114</v>
@@ -2712,13 +2649,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>115</v>
@@ -2792,16 +2729,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F5">
         <v>0.02</v>
@@ -2891,34 +2828,34 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>122</v>
@@ -2939,19 +2876,19 @@
         <v>140</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -2959,22 +2896,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3052,25 +2989,25 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>135</v>
@@ -3100,25 +3037,25 @@
         <v>143</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="X1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
@@ -3126,28 +3063,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
         <v>197</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>197</v>
-      </c>
-      <c r="E2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>199</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3203,28 +3140,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>198</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
         <v>198</v>
-      </c>
-      <c r="E3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>200</v>
       </c>
       <c r="L3">
         <v>10</v>
@@ -3302,10 +3239,10 @@
         <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>56</v>
@@ -3316,13 +3253,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3342,13 +3279,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3368,13 +3305,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -3394,13 +3331,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3442,10 +3379,10 @@
         <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3459,16 +3396,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>12.876519999999999</v>
+        <v>16.289200000000001</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3478,10 +3415,10 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A7BED8-D16A-4858-88BF-19657812A135}">
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -3507,96 +3444,99 @@
         <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>227</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>229</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -3611,7 +3551,7 @@
         <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J2">
         <v>0.01</v>
@@ -3638,7 +3578,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -3659,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="Z2">
+        <v>59</v>
+      </c>
+      <c r="AA2">
         <v>59.5</v>
-      </c>
-      <c r="AA2">
-        <v>59.7</v>
       </c>
       <c r="AB2">
         <v>60.3</v>
@@ -3685,8 +3625,11 @@
       <c r="AH2">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3697,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -3712,7 +3655,7 @@
         <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J3">
         <v>0.01</v>
@@ -3739,7 +3682,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -3760,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="Z3">
+        <v>59</v>
+      </c>
+      <c r="AA3">
         <v>59.5</v>
-      </c>
-      <c r="AA3">
-        <v>59.7</v>
       </c>
       <c r="AB3">
         <v>60.3</v>
@@ -3786,8 +3729,11 @@
       <c r="AH3">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3798,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -3813,7 +3759,7 @@
         <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J4">
         <v>0.01</v>
@@ -3840,7 +3786,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -3861,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="Z4">
+        <v>59</v>
+      </c>
+      <c r="AA4">
         <v>59.5</v>
-      </c>
-      <c r="AA4">
-        <v>59.7</v>
       </c>
       <c r="AB4">
         <v>60.3</v>
@@ -3887,8 +3833,11 @@
       <c r="AH4">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3899,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3914,7 +3863,7 @@
         <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J5">
         <v>0.01</v>
@@ -3941,7 +3890,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -3962,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="Z5">
+        <v>59</v>
+      </c>
+      <c r="AA5">
         <v>59.5</v>
-      </c>
-      <c r="AA5">
-        <v>59.7</v>
       </c>
       <c r="AB5">
         <v>60.3</v>
@@ -3988,8 +3937,11 @@
       <c r="AH5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4000,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -4015,7 +3967,7 @@
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J6">
         <v>0.01</v>
@@ -4042,7 +3994,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>1</v>
@@ -4063,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="Z6">
+        <v>59</v>
+      </c>
+      <c r="AA6">
         <v>59.5</v>
-      </c>
-      <c r="AA6">
-        <v>59.7</v>
       </c>
       <c r="AB6">
         <v>60.3</v>
@@ -4089,8 +4041,11 @@
       <c r="AH6">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4101,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -4116,7 +4071,7 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J7">
         <v>0.01</v>
@@ -4143,7 +4098,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>1</v>
@@ -4164,10 +4119,10 @@
         <v>0</v>
       </c>
       <c r="Z7">
+        <v>59</v>
+      </c>
+      <c r="AA7">
         <v>59.5</v>
-      </c>
-      <c r="AA7">
-        <v>59.7</v>
       </c>
       <c r="AB7">
         <v>60.3</v>
@@ -4190,8 +4145,11 @@
       <c r="AH7">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4202,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -4217,7 +4175,7 @@
         <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J8">
         <v>0.01</v>
@@ -4244,7 +4202,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -4265,10 +4223,10 @@
         <v>0</v>
       </c>
       <c r="Z8">
+        <v>59</v>
+      </c>
+      <c r="AA8">
         <v>59.5</v>
-      </c>
-      <c r="AA8">
-        <v>59.7</v>
       </c>
       <c r="AB8">
         <v>60.3</v>
@@ -4291,8 +4249,11 @@
       <c r="AH8">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -4303,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -4318,7 +4279,7 @@
         <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J9">
         <v>0.01</v>
@@ -4345,7 +4306,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>1</v>
@@ -4366,10 +4327,10 @@
         <v>0</v>
       </c>
       <c r="Z9">
+        <v>59</v>
+      </c>
+      <c r="AA9">
         <v>59.5</v>
-      </c>
-      <c r="AA9">
-        <v>59.7</v>
       </c>
       <c r="AB9">
         <v>60.3</v>
@@ -4392,8 +4353,11 @@
       <c r="AH9">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -4404,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -4419,7 +4383,7 @@
         <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J10">
         <v>0.01</v>
@@ -4446,7 +4410,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -4467,10 +4431,10 @@
         <v>0</v>
       </c>
       <c r="Z10">
+        <v>59</v>
+      </c>
+      <c r="AA10">
         <v>59.5</v>
-      </c>
-      <c r="AA10">
-        <v>59.7</v>
       </c>
       <c r="AB10">
         <v>60.3</v>
@@ -4493,8 +4457,11 @@
       <c r="AH10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -4505,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -4520,7 +4487,7 @@
         <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="J11">
         <v>0.01</v>
@@ -4547,7 +4514,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -4568,10 +4535,10 @@
         <v>0</v>
       </c>
       <c r="Z11">
+        <v>59</v>
+      </c>
+      <c r="AA11">
         <v>59.5</v>
-      </c>
-      <c r="AA11">
-        <v>59.7</v>
       </c>
       <c r="AB11">
         <v>60.3</v>
@@ -4594,8 +4561,11 @@
       <c r="AH11">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -4606,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -4621,7 +4591,7 @@
         <v>60</v>
       </c>
       <c r="I12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J12">
         <v>0.01</v>
@@ -4648,7 +4618,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>1</v>
@@ -4669,10 +4639,10 @@
         <v>0</v>
       </c>
       <c r="Z12">
+        <v>59</v>
+      </c>
+      <c r="AA12">
         <v>59.5</v>
-      </c>
-      <c r="AA12">
-        <v>59.7</v>
       </c>
       <c r="AB12">
         <v>60.3</v>
@@ -4695,8 +4665,11 @@
       <c r="AH12">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -4707,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -4722,7 +4695,7 @@
         <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J13">
         <v>0.01</v>
@@ -4749,7 +4722,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>1</v>
@@ -4770,10 +4743,10 @@
         <v>0</v>
       </c>
       <c r="Z13">
+        <v>59</v>
+      </c>
+      <c r="AA13">
         <v>59.5</v>
-      </c>
-      <c r="AA13">
-        <v>59.7</v>
       </c>
       <c r="AB13">
         <v>60.3</v>
@@ -4796,8 +4769,11 @@
       <c r="AH13">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -4808,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -4823,7 +4799,7 @@
         <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J14">
         <v>0.01</v>
@@ -4850,7 +4826,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>1</v>
@@ -4871,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="Z14">
+        <v>59</v>
+      </c>
+      <c r="AA14">
         <v>59.5</v>
-      </c>
-      <c r="AA14">
-        <v>59.7</v>
       </c>
       <c r="AB14">
         <v>60.3</v>
@@ -4897,8 +4873,11 @@
       <c r="AH14">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -4909,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -4924,7 +4903,7 @@
         <v>60</v>
       </c>
       <c r="I15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J15">
         <v>0.01</v>
@@ -4951,7 +4930,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>1</v>
@@ -4972,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="Z15">
+        <v>59</v>
+      </c>
+      <c r="AA15">
         <v>59.5</v>
-      </c>
-      <c r="AA15">
-        <v>59.7</v>
       </c>
       <c r="AB15">
         <v>60.3</v>
@@ -4998,8 +4977,11 @@
       <c r="AH15">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -5010,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -5025,7 +5007,7 @@
         <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J16">
         <v>0.01</v>
@@ -5052,7 +5034,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>1</v>
@@ -5073,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="Z16">
+        <v>59</v>
+      </c>
+      <c r="AA16">
         <v>59.5</v>
-      </c>
-      <c r="AA16">
-        <v>59.7</v>
       </c>
       <c r="AB16">
         <v>60.3</v>
@@ -5099,8 +5081,11 @@
       <c r="AH16">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -5111,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -5126,7 +5111,7 @@
         <v>60</v>
       </c>
       <c r="I17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J17">
         <v>0.01</v>
@@ -5153,7 +5138,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>1</v>
@@ -5174,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="Z17">
+        <v>59</v>
+      </c>
+      <c r="AA17">
         <v>59.5</v>
-      </c>
-      <c r="AA17">
-        <v>59.7</v>
       </c>
       <c r="AB17">
         <v>60.3</v>
@@ -5200,8 +5185,11 @@
       <c r="AH17">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -5212,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E18">
         <v>9</v>
@@ -5227,7 +5215,7 @@
         <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J18">
         <v>0.01</v>
@@ -5254,7 +5242,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>1</v>
@@ -5275,10 +5263,10 @@
         <v>0</v>
       </c>
       <c r="Z18">
+        <v>59</v>
+      </c>
+      <c r="AA18">
         <v>59.5</v>
-      </c>
-      <c r="AA18">
-        <v>59.7</v>
       </c>
       <c r="AB18">
         <v>60.3</v>
@@ -5301,8 +5289,11 @@
       <c r="AH18">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -5313,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -5328,7 +5319,7 @@
         <v>60</v>
       </c>
       <c r="I19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J19">
         <v>0.01</v>
@@ -5355,7 +5346,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -5376,10 +5367,10 @@
         <v>0</v>
       </c>
       <c r="Z19">
+        <v>59</v>
+      </c>
+      <c r="AA19">
         <v>59.5</v>
-      </c>
-      <c r="AA19">
-        <v>59.7</v>
       </c>
       <c r="AB19">
         <v>60.3</v>
@@ -5402,8 +5393,11 @@
       <c r="AH19">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -5414,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E20">
         <v>9</v>
@@ -5429,7 +5423,7 @@
         <v>60</v>
       </c>
       <c r="I20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J20">
         <v>0.01</v>
@@ -5456,7 +5450,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>1</v>
@@ -5477,10 +5471,10 @@
         <v>0</v>
       </c>
       <c r="Z20">
+        <v>59</v>
+      </c>
+      <c r="AA20">
         <v>59.5</v>
-      </c>
-      <c r="AA20">
-        <v>59.7</v>
       </c>
       <c r="AB20">
         <v>60.3</v>
@@ -5503,8 +5497,11 @@
       <c r="AH20">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -5515,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21">
         <v>9</v>
@@ -5530,7 +5527,7 @@
         <v>60</v>
       </c>
       <c r="I21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J21">
         <v>0.01</v>
@@ -5557,7 +5554,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
       <c r="S21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>1</v>
@@ -5578,10 +5575,10 @@
         <v>0</v>
       </c>
       <c r="Z21">
+        <v>59</v>
+      </c>
+      <c r="AA21">
         <v>59.5</v>
-      </c>
-      <c r="AA21">
-        <v>59.7</v>
       </c>
       <c r="AB21">
         <v>60.3</v>
@@ -5603,6 +5600,9 @@
       </c>
       <c r="AH21">
         <v>0.1</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8151,7 +8151,27 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -8593,13 +8613,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E6">
         <v>8</v>
